--- a/salidas/empresas/CSX.xlsx
+++ b/salidas/empresas/CSX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,54 +447,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>2.166720151901245</v>
+        <v>2.166719198226929</v>
       </c>
       <c r="C3" t="n">
         <v>3.076667070388794</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>2.339648723602295</v>
+        <v>2.33965015411377</v>
       </c>
       <c r="C4" t="n">
         <v>3.322221994400024</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>2.679641723632812</v>
+        <v>2.679643630981445</v>
       </c>
       <c r="C5" t="n">
         <v>3.805000066757202</v>
@@ -558,7 +570,7 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>2.761319398880005</v>
+        <v>2.761318922042847</v>
       </c>
       <c r="C7" t="n">
         <v>3.913332939147949</v>
@@ -596,7 +608,7 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>2.377121210098267</v>
+        <v>2.377120733261108</v>
       </c>
       <c r="C9" t="n">
         <v>3.357778072357178</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>2.582425355911255</v>
+        <v>2.582425117492676</v>
       </c>
       <c r="C10" t="n">
         <v>3.647778034210205</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>2.805819749832153</v>
+        <v>2.805819988250732</v>
       </c>
       <c r="C11" t="n">
         <v>3.963332891464233</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>2.828528165817261</v>
+        <v>2.828527688980103</v>
       </c>
       <c r="C12" t="n">
         <v>3.98444390296936</v>
@@ -691,7 +703,7 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>2.901884794235229</v>
+        <v>2.901882886886597</v>
       </c>
       <c r="C14" t="n">
         <v>4.087778091430664</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>2.976402044296265</v>
+        <v>2.976402282714844</v>
       </c>
       <c r="C15" t="n">
         <v>4.179999828338623</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>3.168659210205078</v>
+        <v>3.168658494949341</v>
       </c>
       <c r="C16" t="n">
         <v>4.449999809265137</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>3.415505170822144</v>
+        <v>3.415505886077881</v>
       </c>
       <c r="C17" t="n">
         <v>4.796667098999023</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>3.604767084121704</v>
+        <v>3.604766368865967</v>
       </c>
       <c r="C18" t="n">
         <v>5.04888916015625</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>3.576208114624023</v>
+        <v>3.57620644569397</v>
       </c>
       <c r="C19" t="n">
         <v>5.008889198303223</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>3.761045932769775</v>
+        <v>3.761048078536987</v>
       </c>
       <c r="C20" t="n">
         <v>5.267777919769287</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>3.264497041702271</v>
+        <v>3.264498472213745</v>
       </c>
       <c r="C21" t="n">
         <v>4.555555820465088</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>3.402243852615356</v>
+        <v>3.402243614196777</v>
       </c>
       <c r="C22" t="n">
         <v>4.747777938842773</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>3.564672231674194</v>
+        <v>3.564671993255615</v>
       </c>
       <c r="C23" t="n">
         <v>4.974443912506104</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>3.356348514556885</v>
+        <v>3.356348991394043</v>
       </c>
       <c r="C24" t="n">
         <v>4.666666984558105</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>3.514577150344849</v>
+        <v>3.514578104019165</v>
       </c>
       <c r="C25" t="n">
         <v>4.886666774749756</v>
@@ -938,7 +950,7 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>3.888444423675537</v>
+        <v>3.888444900512695</v>
       </c>
       <c r="C27" t="n">
         <v>5.391110897064209</v>
@@ -976,7 +988,7 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>5.044881343841553</v>
+        <v>5.044880867004395</v>
       </c>
       <c r="C29" t="n">
         <v>6.994443893432617</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>5.54936408996582</v>
+        <v>5.549366474151611</v>
       </c>
       <c r="C30" t="n">
         <v>7.673333168029785</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>5.047143459320068</v>
+        <v>5.047142028808594</v>
       </c>
       <c r="C31" t="n">
         <v>6.978888988494873</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>5.430439949035645</v>
+        <v>5.430440902709961</v>
       </c>
       <c r="C32" t="n">
         <v>7.508889198303223</v>
@@ -1071,7 +1083,7 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>4.400282859802246</v>
+        <v>4.400283813476562</v>
       </c>
       <c r="C34" t="n">
         <v>6.063333034515381</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>3.686659574508667</v>
+        <v>3.686656951904297</v>
       </c>
       <c r="C35" t="n">
         <v>5.079999923706055</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>3.021027565002441</v>
+        <v>3.021026849746704</v>
       </c>
       <c r="C36" t="n">
         <v>4.137777805328369</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>2.634069681167603</v>
+        <v>2.634070634841919</v>
       </c>
       <c r="C37" t="n">
         <v>3.607778072357178</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>2.349327802658081</v>
+        <v>2.349327564239502</v>
       </c>
       <c r="C38" t="n">
         <v>3.217777967453003</v>
@@ -1185,7 +1197,7 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>2.114436864852905</v>
+        <v>2.114437103271484</v>
       </c>
       <c r="C40" t="n">
         <v>2.872221946716309</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>2.420356750488281</v>
+        <v>2.420355558395386</v>
       </c>
       <c r="C41" t="n">
         <v>3.287777900695801</v>
@@ -1248,11 +1260,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>2.617141723632812</v>
+        <v>2.617142200469971</v>
       </c>
       <c r="C42" t="n">
         <v>3.528888940811157</v>
@@ -1273,11 +1285,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>2.853641033172607</v>
+        <v>2.853641510009766</v>
       </c>
       <c r="C43" t="n">
         <v>3.847778081893921</v>
@@ -1298,11 +1310,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>3.306038379669189</v>
+        <v>3.306037664413452</v>
       </c>
       <c r="C44" t="n">
         <v>4.457777976989746</v>
@@ -1323,11 +1335,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>3.520146608352661</v>
+        <v>3.520146131515503</v>
       </c>
       <c r="C45" t="n">
         <v>4.722221851348877</v>
@@ -1348,11 +1360,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>3.467137336730957</v>
+        <v>3.467138528823853</v>
       </c>
       <c r="C46" t="n">
         <v>4.651111125946045</v>
@@ -1373,11 +1385,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>3.493643045425415</v>
+        <v>3.493643522262573</v>
       </c>
       <c r="C47" t="n">
         <v>4.686666965484619</v>
@@ -1398,11 +1410,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>3.950733423233032</v>
+        <v>3.950731039047241</v>
       </c>
       <c r="C48" t="n">
         <v>5.275556087493896</v>
@@ -1423,11 +1435,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>4.03477144241333</v>
+        <v>4.034773826599121</v>
       </c>
       <c r="C49" t="n">
         <v>5.387777805328369</v>
@@ -1448,11 +1460,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>3.566310405731201</v>
+        <v>3.566310167312622</v>
       </c>
       <c r="C50" t="n">
         <v>4.762221813201904</v>
@@ -1473,11 +1485,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>3.969336986541748</v>
+        <v>3.969337940216064</v>
       </c>
       <c r="C51" t="n">
         <v>5.273333072662354</v>
@@ -1502,11 +1514,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>4.257043838500977</v>
+        <v>4.257045269012451</v>
       </c>
       <c r="C52" t="n">
         <v>5.655556201934814</v>
@@ -1531,7 +1543,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
@@ -1560,11 +1572,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>4.390827655792236</v>
+        <v>4.390827178955078</v>
       </c>
       <c r="C54" t="n">
         <v>5.805555820465088</v>
@@ -1589,7 +1601,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
@@ -1618,11 +1630,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>4.430323600769043</v>
+        <v>4.430323123931885</v>
       </c>
       <c r="C56" t="n">
         <v>5.857778072357178</v>
@@ -1647,11 +1659,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>4.213371276855469</v>
+        <v>4.213371753692627</v>
       </c>
       <c r="C57" t="n">
         <v>5.543333053588867</v>
@@ -1676,11 +1688,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>4.671954154968262</v>
+        <v>4.671953678131104</v>
       </c>
       <c r="C58" t="n">
         <v>6.146667003631592</v>
@@ -1705,7 +1717,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
@@ -1734,11 +1746,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>5.157263278961182</v>
+        <v>5.157262325286865</v>
       </c>
       <c r="C60" t="n">
         <v>6.756667137145996</v>
@@ -1763,11 +1775,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>5.479538440704346</v>
+        <v>5.479537963867188</v>
       </c>
       <c r="C61" t="n">
         <v>7.17888879776001</v>
@@ -1792,11 +1804,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>5.987547397613525</v>
+        <v>5.987547874450684</v>
       </c>
       <c r="C62" t="n">
         <v>7.844443798065186</v>
@@ -1821,11 +1833,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>6.35496997833252</v>
+        <v>6.354968070983887</v>
       </c>
       <c r="C63" t="n">
         <v>8.29555606842041</v>
@@ -1850,11 +1862,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>6.6903395652771</v>
+        <v>6.690336227416992</v>
       </c>
       <c r="C64" t="n">
         <v>8.733332633972168</v>
@@ -1879,11 +1891,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>6.697999954223633</v>
+        <v>6.698001384735107</v>
       </c>
       <c r="C65" t="n">
         <v>8.743332862854004</v>
@@ -1908,7 +1920,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
@@ -1937,11 +1949,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>6.727031707763672</v>
+        <v>6.72703218460083</v>
       </c>
       <c r="C67" t="n">
         <v>8.739999771118164</v>
@@ -1966,11 +1978,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>6.303706645965576</v>
+        <v>6.303707122802734</v>
       </c>
       <c r="C68" t="n">
         <v>8.189999580383301</v>
@@ -1995,11 +2007,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>5.660617828369141</v>
+        <v>5.660619258880615</v>
       </c>
       <c r="C69" t="n">
         <v>7.313333034515381</v>
@@ -2024,11 +2036,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>4.816944599151611</v>
+        <v>4.816943645477295</v>
       </c>
       <c r="C70" t="n">
         <v>6.22333288192749</v>
@@ -2053,11 +2065,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>5.730280876159668</v>
+        <v>5.730279922485352</v>
       </c>
       <c r="C71" t="n">
         <v>7.403333187103271</v>
@@ -2082,7 +2094,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
@@ -2111,11 +2123,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>5.466373920440674</v>
+        <v>5.466372966766357</v>
       </c>
       <c r="C73" t="n">
         <v>7.019999980926514</v>
@@ -2140,11 +2152,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>5.85312032699585</v>
+        <v>5.853119373321533</v>
       </c>
       <c r="C74" t="n">
         <v>7.516666889190674</v>
@@ -2169,11 +2181,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>5.483776092529297</v>
+        <v>5.483774662017822</v>
       </c>
       <c r="C75" t="n">
         <v>7.00333309173584</v>
@@ -2198,7 +2210,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
@@ -2227,7 +2239,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
@@ -2256,11 +2268,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>5.488411426544189</v>
+        <v>5.488409996032715</v>
       </c>
       <c r="C78" t="n">
         <v>6.963333129882812</v>
@@ -2285,11 +2297,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>5.874622821807861</v>
+        <v>5.87462329864502</v>
       </c>
       <c r="C79" t="n">
         <v>7.453332901000977</v>
@@ -2314,11 +2326,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>6.027006149291992</v>
+        <v>6.027005672454834</v>
       </c>
       <c r="C80" t="n">
         <v>7.646667003631592</v>
@@ -2343,11 +2355,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>5.93751335144043</v>
+        <v>5.937515258789062</v>
       </c>
       <c r="C81" t="n">
         <v>7.486667156219482</v>
@@ -2372,11 +2384,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>5.485461711883545</v>
+        <v>5.485462665557861</v>
       </c>
       <c r="C82" t="n">
         <v>6.916666984558105</v>
@@ -2401,11 +2413,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>5.411440849304199</v>
+        <v>5.411438941955566</v>
       </c>
       <c r="C83" t="n">
         <v>6.823332786560059</v>
@@ -2430,11 +2442,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>5.260550022125244</v>
+        <v>5.260548114776611</v>
       </c>
       <c r="C84" t="n">
         <v>6.586667060852051</v>
@@ -2459,11 +2471,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>5.252562522888184</v>
+        <v>5.252565383911133</v>
       </c>
       <c r="C85" t="n">
         <v>6.576666831970215</v>
@@ -2488,11 +2500,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>5.864874362945557</v>
+        <v>5.864873886108398</v>
       </c>
       <c r="C86" t="n">
         <v>7.343332767486572</v>
@@ -2517,11 +2529,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>6.145859241485596</v>
+        <v>6.145859718322754</v>
       </c>
       <c r="C87" t="n">
         <v>7.646667003631592</v>
@@ -2546,11 +2558,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>6.598626136779785</v>
+        <v>6.598626613616943</v>
       </c>
       <c r="C88" t="n">
         <v>8.210000038146973</v>
@@ -2575,11 +2587,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>6.587910652160645</v>
+        <v>6.587911128997803</v>
       </c>
       <c r="C89" t="n">
         <v>8.196666717529297</v>
@@ -2604,11 +2616,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>6.79429817199707</v>
+        <v>6.794297218322754</v>
       </c>
       <c r="C90" t="n">
         <v>8.403332710266113</v>
@@ -2633,7 +2645,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
@@ -2662,11 +2674,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>6.686497211456299</v>
+        <v>6.68649435043335</v>
       </c>
       <c r="C92" t="n">
         <v>8.270000457763672</v>
@@ -2691,11 +2703,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>6.672937393188477</v>
+        <v>6.672937870025635</v>
       </c>
       <c r="C93" t="n">
         <v>8.203332901000977</v>
@@ -2720,11 +2732,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>6.979334831237793</v>
+        <v>6.979333400726318</v>
       </c>
       <c r="C94" t="n">
         <v>8.579999923706055</v>
@@ -2749,11 +2761,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>7.066100120544434</v>
+        <v>7.066100597381592</v>
       </c>
       <c r="C95" t="n">
         <v>8.686667442321777</v>
@@ -2778,11 +2790,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>7.434892177581787</v>
+        <v>7.434889793395996</v>
       </c>
       <c r="C96" t="n">
         <v>9.090000152587891</v>
@@ -2807,11 +2819,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>7.843850135803223</v>
+        <v>7.843854427337646</v>
       </c>
       <c r="C97" t="n">
         <v>9.590000152587891</v>
@@ -2836,11 +2848,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>7.336742401123047</v>
+        <v>7.33674144744873</v>
       </c>
       <c r="C98" t="n">
         <v>8.970000267028809</v>
@@ -2865,11 +2877,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>7.596578121185303</v>
+        <v>7.596576690673828</v>
       </c>
       <c r="C99" t="n">
         <v>9.236666679382324</v>
@@ -2894,7 +2906,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
@@ -2923,11 +2935,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>7.736393451690674</v>
+        <v>7.736391544342041</v>
       </c>
       <c r="C101" t="n">
         <v>9.40666675567627</v>
@@ -2952,11 +2964,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>8.103914260864258</v>
+        <v>8.103913307189941</v>
       </c>
       <c r="C102" t="n">
         <v>9.800000190734863</v>
@@ -2981,11 +2993,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>8.492568016052246</v>
+        <v>8.49256706237793</v>
       </c>
       <c r="C103" t="n">
         <v>10.27000045776367</v>
@@ -3010,11 +3022,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>8.247246742248535</v>
+        <v>8.247247695922852</v>
       </c>
       <c r="C104" t="n">
         <v>9.973333358764648</v>
@@ -3039,11 +3051,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>8.564583778381348</v>
+        <v>8.564579010009766</v>
       </c>
       <c r="C105" t="n">
         <v>10.3033332824707</v>
@@ -3068,7 +3080,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
@@ -3097,11 +3109,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>9.872404098510742</v>
+        <v>9.872403144836426</v>
       </c>
       <c r="C107" t="n">
         <v>11.87666702270508</v>
@@ -3126,11 +3138,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>10.1535816192627</v>
+        <v>10.15357971191406</v>
       </c>
       <c r="C108" t="n">
         <v>12.16333293914795</v>
@@ -3155,11 +3167,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>10.08123302459717</v>
+        <v>10.08123683929443</v>
       </c>
       <c r="C109" t="n">
         <v>12.07666683197021</v>
@@ -3184,11 +3196,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>9.265941619873047</v>
+        <v>9.265945434570312</v>
       </c>
       <c r="C110" t="n">
         <v>11.10000038146973</v>
@@ -3213,11 +3225,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>9.590119361877441</v>
+        <v>9.590121269226074</v>
       </c>
       <c r="C111" t="n">
         <v>11.43666744232178</v>
@@ -3242,11 +3254,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>9.25749683380127</v>
+        <v>9.257497787475586</v>
       </c>
       <c r="C112" t="n">
         <v>11.03999996185303</v>
@@ -3271,7 +3283,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
@@ -3300,11 +3312,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>9.57538890838623</v>
+        <v>9.575386047363281</v>
       </c>
       <c r="C114" t="n">
         <v>11.35999965667725</v>
@@ -3329,11 +3341,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>9.17359733581543</v>
+        <v>9.173603057861328</v>
       </c>
       <c r="C115" t="n">
         <v>10.88333320617676</v>
@@ -3358,11 +3370,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>8.788677215576172</v>
+        <v>8.788678169250488</v>
       </c>
       <c r="C116" t="n">
         <v>10.42666721343994</v>
@@ -3387,11 +3399,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>7.745773315429688</v>
+        <v>7.745772838592529</v>
       </c>
       <c r="C117" t="n">
         <v>9.126667022705078</v>
@@ -3416,11 +3428,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>7.609984397888184</v>
+        <v>7.609984874725342</v>
       </c>
       <c r="C118" t="n">
         <v>8.966667175292969</v>
@@ -3445,7 +3457,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
@@ -3474,11 +3486,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>8.092996597290039</v>
+        <v>8.093002319335938</v>
       </c>
       <c r="C120" t="n">
         <v>9.476667404174805</v>
@@ -3503,11 +3515,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>7.387031555175781</v>
+        <v>7.387032985687256</v>
       </c>
       <c r="C121" t="n">
         <v>8.649999618530273</v>
@@ -3532,11 +3544,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>6.552966594696045</v>
+        <v>6.552965641021729</v>
       </c>
       <c r="C122" t="n">
         <v>7.673333168029785</v>
@@ -3561,11 +3573,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>6.922672271728516</v>
+        <v>6.922671794891357</v>
       </c>
       <c r="C123" t="n">
         <v>8.046667098999023</v>
@@ -3590,11 +3602,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>7.384372711181641</v>
+        <v>7.384373664855957</v>
       </c>
       <c r="C124" t="n">
         <v>8.583333015441895</v>
@@ -3619,11 +3631,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>7.820266246795654</v>
+        <v>7.820268630981445</v>
       </c>
       <c r="C125" t="n">
         <v>9.090000152587891</v>
@@ -3648,11 +3660,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>7.632568836212158</v>
+        <v>7.632567882537842</v>
       </c>
       <c r="C126" t="n">
         <v>8.810000419616699</v>
@@ -3677,11 +3689,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>7.531489372253418</v>
+        <v>7.531491279602051</v>
       </c>
       <c r="C127" t="n">
         <v>8.693332672119141</v>
@@ -3706,11 +3718,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>8.181257247924805</v>
+        <v>8.181260108947754</v>
       </c>
       <c r="C128" t="n">
         <v>9.443332672119141</v>
@@ -3735,7 +3747,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
@@ -3764,11 +3776,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>8.864523887634277</v>
+        <v>8.864521980285645</v>
       </c>
       <c r="C130" t="n">
         <v>10.16666698455811</v>
@@ -3793,11 +3805,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>8.867431640625</v>
+        <v>8.867426872253418</v>
       </c>
       <c r="C131" t="n">
         <v>10.17000007629395</v>
@@ -3822,11 +3834,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>10.46133232116699</v>
+        <v>10.46132850646973</v>
       </c>
       <c r="C132" t="n">
         <v>11.93666744232178</v>
@@ -3851,11 +3863,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>10.4963903427124</v>
+        <v>10.49638748168945</v>
       </c>
       <c r="C133" t="n">
         <v>11.9766674041748</v>
@@ -3880,11 +3892,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>13.55211162567139</v>
+        <v>13.55211353302002</v>
       </c>
       <c r="C134" t="n">
         <v>15.46333312988281</v>
@@ -3909,11 +3921,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>14.23954010009766</v>
+        <v>14.23954582214355</v>
       </c>
       <c r="C135" t="n">
         <v>16.18666648864746</v>
@@ -3938,7 +3950,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
@@ -3967,11 +3979,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>14.90812397003174</v>
+        <v>14.90812492370605</v>
       </c>
       <c r="C137" t="n">
         <v>16.9466667175293</v>
@@ -3996,11 +4008,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>15.94387626647949</v>
+        <v>15.94387722015381</v>
       </c>
       <c r="C138" t="n">
         <v>18.05666732788086</v>
@@ -4025,11 +4037,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>16.05866622924805</v>
+        <v>16.05866813659668</v>
       </c>
       <c r="C139" t="n">
         <v>18.18666648864746</v>
@@ -4054,11 +4066,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>14.52226257324219</v>
+        <v>14.52226638793945</v>
       </c>
       <c r="C140" t="n">
         <v>16.4466667175293</v>
@@ -4083,11 +4095,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>14.83533382415771</v>
+        <v>14.83532905578613</v>
       </c>
       <c r="C141" t="n">
         <v>16.73333358764648</v>
@@ -4112,11 +4124,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>16.03515434265137</v>
+        <v>16.03515815734863</v>
       </c>
       <c r="C142" t="n">
         <v>18.08666610717773</v>
@@ -4141,11 +4153,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>14.90330028533936</v>
+        <v>14.90329837799072</v>
       </c>
       <c r="C143" t="n">
         <v>16.80999946594238</v>
@@ -4170,11 +4182,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>16.53893852233887</v>
+        <v>16.5389404296875</v>
       </c>
       <c r="C144" t="n">
         <v>18.58333206176758</v>
@@ -4199,11 +4211,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>16.31940650939941</v>
+        <v>16.31941795349121</v>
       </c>
       <c r="C145" t="n">
         <v>18.33666610717773</v>
@@ -4228,11 +4240,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>16.84153366088867</v>
+        <v>16.84154319763184</v>
       </c>
       <c r="C146" t="n">
         <v>18.92333221435547</v>
@@ -4257,11 +4269,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>16.00057983398438</v>
+        <v>16.00058364868164</v>
       </c>
       <c r="C147" t="n">
         <v>17.90666770935059</v>
@@ -4286,11 +4298,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>16.59330940246582</v>
+        <v>16.59330558776855</v>
       </c>
       <c r="C148" t="n">
         <v>18.56999969482422</v>
@@ -4315,11 +4327,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>17.68940353393555</v>
+        <v>17.68939971923828</v>
       </c>
       <c r="C149" t="n">
         <v>19.79666709899902</v>
@@ -4344,11 +4356,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>19.3222827911377</v>
+        <v>19.32228660583496</v>
       </c>
       <c r="C150" t="n">
         <v>21.54999923706055</v>
@@ -4373,11 +4385,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>19.06226921081543</v>
+        <v>19.0622673034668</v>
       </c>
       <c r="C151" t="n">
         <v>21.26000022888184</v>
@@ -4402,11 +4414,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>21.1245059967041</v>
+        <v>21.12451362609863</v>
       </c>
       <c r="C152" t="n">
         <v>23.55999946594238</v>
@@ -4431,11 +4443,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>22.22995758056641</v>
+        <v>22.22996139526367</v>
       </c>
       <c r="C153" t="n">
         <v>24.71999931335449</v>
@@ -4460,11 +4472,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>22.19698333740234</v>
+        <v>22.19698143005371</v>
       </c>
       <c r="C154" t="n">
         <v>24.6833324432373</v>
@@ -4489,11 +4501,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>20.64124488830566</v>
+        <v>20.6412467956543</v>
       </c>
       <c r="C155" t="n">
         <v>22.95333290100098</v>
@@ -4518,11 +4530,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>21.83736610412598</v>
+        <v>21.83736228942871</v>
       </c>
       <c r="C156" t="n">
         <v>24.20999908447266</v>
@@ -4547,11 +4559,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>18.68037414550781</v>
+        <v>18.68037033081055</v>
       </c>
       <c r="C157" t="n">
         <v>20.70999908447266</v>
@@ -4576,11 +4588,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>19.75375175476074</v>
+        <v>19.75374794006348</v>
       </c>
       <c r="C158" t="n">
         <v>21.89999961853027</v>
@@ -4605,11 +4617,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>21.92170333862305</v>
+        <v>21.92169952392578</v>
       </c>
       <c r="C159" t="n">
         <v>24.22333335876465</v>
@@ -4634,7 +4646,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
@@ -4663,11 +4675,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>24.02125930786133</v>
+        <v>24.02126312255859</v>
       </c>
       <c r="C161" t="n">
         <v>26.54333305358887</v>
@@ -4692,11 +4704,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>22.53783798217773</v>
+        <v>22.5378360748291</v>
       </c>
       <c r="C162" t="n">
         <v>24.82333374023438</v>
@@ -4721,11 +4733,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>23.41550254821777</v>
+        <v>23.41550064086914</v>
       </c>
       <c r="C163" t="n">
         <v>25.79000091552734</v>
@@ -4750,7 +4762,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
@@ -4779,11 +4791,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>20.35786819458008</v>
+        <v>20.35786247253418</v>
       </c>
       <c r="C165" t="n">
         <v>22.34000015258789</v>
@@ -4808,11 +4820,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>21.04132270812988</v>
+        <v>21.04132461547852</v>
       </c>
       <c r="C166" t="n">
         <v>23.09000015258789</v>
@@ -4837,11 +4849,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>21.34507369995117</v>
+        <v>21.3450756072998</v>
       </c>
       <c r="C167" t="n">
         <v>23.42333221435547</v>
@@ -4866,11 +4878,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>21.8035774230957</v>
+        <v>21.80357551574707</v>
       </c>
       <c r="C168" t="n">
         <v>23.84666633605957</v>
@@ -4895,11 +4907,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>22.05349349975586</v>
+        <v>22.05349540710449</v>
       </c>
       <c r="C169" t="n">
         <v>24.1200008392334</v>
@@ -4924,11 +4936,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>23.26649284362793</v>
+        <v>23.26649475097656</v>
       </c>
       <c r="C170" t="n">
         <v>25.4466667175293</v>
@@ -4953,11 +4965,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>21.5457592010498</v>
+        <v>21.54576301574707</v>
       </c>
       <c r="C171" t="n">
         <v>23.48333358764648</v>
@@ -4982,11 +4994,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>17.52409172058105</v>
+        <v>17.52408981323242</v>
       </c>
       <c r="C172" t="n">
         <v>19.10000038146973</v>
@@ -5011,7 +5023,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
@@ -5040,11 +5052,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>21.96895599365234</v>
+        <v>21.96895980834961</v>
       </c>
       <c r="C174" t="n">
         <v>23.86000061035156</v>
@@ -5069,7 +5081,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -5098,7 +5110,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
@@ -5127,11 +5139,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>23.54705429077148</v>
+        <v>23.54705810546875</v>
       </c>
       <c r="C177" t="n">
         <v>25.48666763305664</v>
@@ -5156,11 +5168,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>23.91969680786133</v>
+        <v>23.9196949005127</v>
       </c>
       <c r="C178" t="n">
         <v>25.88999938964844</v>
@@ -5185,11 +5197,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>24.31081008911133</v>
+        <v>24.31081199645996</v>
       </c>
       <c r="C179" t="n">
         <v>26.31333351135254</v>
@@ -5214,11 +5226,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>27.81069946289062</v>
+        <v>27.81070327758789</v>
       </c>
       <c r="C180" t="n">
         <v>30.01666641235352</v>
@@ -5243,11 +5255,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>28.02688980102539</v>
+        <v>28.02688598632812</v>
       </c>
       <c r="C181" t="n">
         <v>30.25</v>
@@ -5272,11 +5284,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>26.48579406738281</v>
+        <v>26.48579025268555</v>
       </c>
       <c r="C182" t="n">
         <v>28.58666610717773</v>
@@ -5301,11 +5313,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>28.3589973449707</v>
+        <v>28.35899925231934</v>
       </c>
       <c r="C183" t="n">
         <v>30.51666641235352</v>
@@ -5330,11 +5342,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>29.86756134033203</v>
+        <v>29.86755752563477</v>
       </c>
       <c r="C184" t="n">
         <v>32.13999938964844</v>
@@ -5359,11 +5371,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>31.20883750915527</v>
+        <v>31.20883941650391</v>
       </c>
       <c r="C185" t="n">
         <v>33.58333206176758</v>
@@ -5388,11 +5400,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>31.10038757324219</v>
+        <v>31.10038185119629</v>
       </c>
       <c r="C186" t="n">
         <v>33.37333297729492</v>
@@ -5417,11 +5429,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>29.8951416015625</v>
+        <v>29.89513969421387</v>
       </c>
       <c r="C187" t="n">
         <v>32.08000183105469</v>
@@ -5446,7 +5458,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
@@ -5475,11 +5487,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>30.39900588989258</v>
+        <v>30.39900970458984</v>
       </c>
       <c r="C189" t="n">
         <v>32.52999877929688</v>
@@ -5504,11 +5516,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>27.79177284240723</v>
+        <v>27.79177665710449</v>
       </c>
       <c r="C190" t="n">
         <v>29.73999977111816</v>
@@ -5533,11 +5545,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>33.80055236816406</v>
+        <v>33.80055999755859</v>
       </c>
       <c r="C191" t="n">
         <v>36.16999816894531</v>
@@ -5562,11 +5574,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>32.47438812255859</v>
+        <v>32.47438049316406</v>
       </c>
       <c r="C192" t="n">
         <v>34.65999984741211</v>
@@ -5591,7 +5603,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
@@ -5620,7 +5632,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
@@ -5649,11 +5661,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>31.86651420593262</v>
+        <v>31.86652183532715</v>
       </c>
       <c r="C195" t="n">
         <v>33.90999984741211</v>
@@ -5678,11 +5690,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>35.19318771362305</v>
+        <v>35.19319152832031</v>
       </c>
       <c r="C196" t="n">
         <v>37.45000076293945</v>
@@ -5707,11 +5719,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>32.27060699462891</v>
+        <v>32.27059555053711</v>
       </c>
       <c r="C197" t="n">
         <v>34.34000015258789</v>
@@ -5736,11 +5748,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>29.96917152404785</v>
+        <v>29.96916770935059</v>
       </c>
       <c r="C198" t="n">
         <v>31.79000091552734</v>
@@ -5765,11 +5777,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>27.39553451538086</v>
+        <v>27.39553642272949</v>
       </c>
       <c r="C199" t="n">
         <v>29.05999946594238</v>
@@ -5794,7 +5806,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
@@ -5823,11 +5835,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>29.92865943908691</v>
+        <v>29.92865753173828</v>
       </c>
       <c r="C201" t="n">
         <v>31.64999961853027</v>
@@ -5852,11 +5864,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>25.19113731384277</v>
+        <v>25.19113159179688</v>
       </c>
       <c r="C202" t="n">
         <v>26.63999938964844</v>
@@ -5881,11 +5893,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>27.47951889038086</v>
+        <v>27.47951698303223</v>
       </c>
       <c r="C203" t="n">
         <v>29.05999946594238</v>
@@ -5910,11 +5922,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>31.00991439819336</v>
+        <v>31.00991058349609</v>
       </c>
       <c r="C204" t="n">
         <v>32.68999862670898</v>
@@ -5939,11 +5951,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>29.3878002166748</v>
+        <v>29.38780403137207</v>
       </c>
       <c r="C205" t="n">
         <v>30.97999954223633</v>
@@ -5968,11 +5980,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>29.33089065551758</v>
+        <v>29.33088874816895</v>
       </c>
       <c r="C206" t="n">
         <v>30.92000007629395</v>
@@ -5997,11 +6009,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>29.02682495117188</v>
+        <v>29.02681922912598</v>
       </c>
       <c r="C207" t="n">
         <v>30.48999977111816</v>
@@ -6026,11 +6038,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>28.50321388244629</v>
+        <v>28.50321769714355</v>
       </c>
       <c r="C208" t="n">
         <v>29.94000053405762</v>
@@ -6055,7 +6067,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
@@ -6084,11 +6096,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>29.30280685424805</v>
+        <v>29.30280303955078</v>
       </c>
       <c r="C210" t="n">
         <v>30.67000007629395</v>
@@ -6113,11 +6125,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>32.57989883422852</v>
+        <v>32.57989501953125</v>
       </c>
       <c r="C211" t="n">
         <v>34.09999847412109</v>
@@ -6142,11 +6154,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>31.83466720581055</v>
+        <v>31.83466911315918</v>
       </c>
       <c r="C212" t="n">
         <v>33.31999969482422</v>
@@ -6171,11 +6183,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>28.95734024047852</v>
+        <v>28.95733833312988</v>
       </c>
       <c r="C213" t="n">
         <v>30.20000076293945</v>
@@ -6200,11 +6212,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>29.48470878601074</v>
+        <v>29.48470687866211</v>
       </c>
       <c r="C214" t="n">
         <v>30.75</v>
@@ -6229,11 +6241,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>28.62174034118652</v>
+        <v>28.62174224853516</v>
       </c>
       <c r="C215" t="n">
         <v>29.85000038146973</v>
@@ -6258,11 +6270,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>31.07759666442871</v>
+        <v>31.07759094238281</v>
       </c>
       <c r="C216" t="n">
         <v>32.29999923706055</v>
@@ -6287,7 +6299,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6316,11 +6328,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>34.34891128540039</v>
+        <v>34.34892272949219</v>
       </c>
       <c r="C218" t="n">
         <v>35.70000076293945</v>
@@ -6345,11 +6357,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>36.61991500854492</v>
+        <v>36.61991119384766</v>
       </c>
       <c r="C219" t="n">
         <v>37.93999862670898</v>
@@ -6374,11 +6386,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>35.78018188476562</v>
+        <v>35.78017807006836</v>
       </c>
       <c r="C220" t="n">
         <v>37.06999969482422</v>
@@ -6403,11 +6415,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>32.06414031982422</v>
+        <v>32.06413650512695</v>
       </c>
       <c r="C221" t="n">
         <v>33.22000122070312</v>
@@ -6432,7 +6444,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6461,11 +6473,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>32.40290069580078</v>
+        <v>32.40290451049805</v>
       </c>
       <c r="C223" t="n">
         <v>33.45000076293945</v>
@@ -6490,11 +6502,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>34.00125122070312</v>
+        <v>34.00124359130859</v>
       </c>
       <c r="C224" t="n">
         <v>35.09999847412109</v>
@@ -6519,11 +6531,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>33.31501770019531</v>
+        <v>33.31502151489258</v>
       </c>
       <c r="C225" t="n">
         <v>34.27000045776367</v>
@@ -6548,11 +6560,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>33.56777572631836</v>
+        <v>33.56777191162109</v>
       </c>
       <c r="C226" t="n">
         <v>34.52999877929688</v>
@@ -6577,7 +6589,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6606,11 +6618,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>35.64843368530273</v>
+        <v>35.64842987060547</v>
       </c>
       <c r="C228" t="n">
         <v>36.54999923706055</v>
@@ -6635,11 +6647,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>31.47400665283203</v>
+        <v>31.4740047454834</v>
       </c>
       <c r="C229" t="n">
         <v>32.27000045776367</v>
@@ -6664,11 +6676,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>32.0592041015625</v>
+        <v>32.05920028686523</v>
       </c>
       <c r="C230" t="n">
         <v>32.86999893188477</v>
@@ -6693,11 +6705,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>31.34772682189941</v>
+        <v>31.34772872924805</v>
       </c>
       <c r="C231" t="n">
         <v>32.0099983215332</v>
@@ -6722,7 +6734,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6751,11 +6763,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>27.48924446105957</v>
+        <v>27.48924255371094</v>
       </c>
       <c r="C233" t="n">
         <v>28.06999969482422</v>
@@ -6780,11 +6792,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>31.06494903564453</v>
+        <v>31.06495094299316</v>
       </c>
       <c r="C234" t="n">
         <v>31.59000015258789</v>
@@ -6809,7 +6821,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6838,11 +6850,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>34.94929885864258</v>
+        <v>34.94929504394531</v>
       </c>
       <c r="C236" t="n">
         <v>35.54000091552734</v>
@@ -6867,7 +6879,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6896,7 +6908,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6925,7 +6937,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6954,11 +6966,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>35.04029846191406</v>
+        <v>35.0402946472168</v>
       </c>
       <c r="C240" t="n">
         <v>35.36000061035156</v>
@@ -6983,11 +6995,11 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>35.92224884033203</v>
+        <v>35.92224502563477</v>
       </c>
       <c r="C241" t="n">
         <v>36.25</v>
@@ -7012,11 +7024,11 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>37.4185905456543</v>
+        <v>37.41859436035156</v>
       </c>
       <c r="C242" t="n">
         <v>37.7599983215332</v>
@@ -7041,7 +7053,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -7070,7 +7082,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7099,7 +7111,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7128,7 +7140,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7157,7 +7169,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7186,7 +7198,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7215,7 +7227,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7244,32 +7256,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>47.18999862670898</v>
+        <v>46.95000076293945</v>
       </c>
       <c r="C250" t="n">
-        <v>47.18999862670898</v>
+        <v>46.95000076293945</v>
       </c>
       <c r="D250" t="n">
-        <v>179650500</v>
+        <v>189204300</v>
       </c>
       <c r="E250" t="n">
         <v>1.73</v>
       </c>
       <c r="F250" t="n">
-        <v>27.277455853589</v>
+        <v>27.13872876470488</v>
       </c>
       <c r="G250" t="n">
         <v>1852474917</v>
       </c>
       <c r="H250" t="n">
-        <v>87418288789.24284</v>
+        <v>86973698766.4762</v>
       </c>
       <c r="I250" t="n">
-        <v>0.0969786410338748</v>
+        <v>0.1021359578279245</v>
       </c>
     </row>
   </sheetData>
@@ -7301,75 +7313,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39445</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39535</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>39918</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7405,13 +7417,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39536</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39626</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40009</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7447,13 +7459,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39627</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39717</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40106</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7489,13 +7501,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39718</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39808</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40228</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7522,7 +7534,7 @@
       <c r="I5" t="n">
         <v>0.3711111111111111</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>40228</v>
       </c>
       <c r="K5" t="n">
@@ -7535,13 +7547,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39809</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>39899</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>39918</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7568,7 +7580,7 @@
       <c r="I6" t="n">
         <v>0.3455555555555556</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>40228</v>
       </c>
       <c r="K6" t="n">
@@ -7581,13 +7593,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>39900</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>39990</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40009</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7614,7 +7626,7 @@
       <c r="I7" t="n">
         <v>0.3288888888888889</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40228</v>
       </c>
       <c r="K7" t="n">
@@ -7627,13 +7639,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>39991</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40081</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40106</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7660,7 +7672,7 @@
       <c r="I8" t="n">
         <v>0.3066666666666666</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40228</v>
       </c>
       <c r="K8" t="n">
@@ -7673,13 +7685,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40082</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40172</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40228</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7706,7 +7718,7 @@
       <c r="I9" t="n">
         <v>0.3233333333333334</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40228</v>
       </c>
       <c r="K9" t="n">
@@ -7719,13 +7731,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40173</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40263</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40287</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7752,7 +7764,7 @@
       <c r="I10" t="n">
         <v>0.3411111111111111</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40287</v>
       </c>
       <c r="K10" t="n">
@@ -7765,13 +7777,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40264</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40354</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40374</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7798,7 +7810,7 @@
       <c r="I11" t="n">
         <v>0.3733333333333334</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40374</v>
       </c>
       <c r="K11" t="n">
@@ -7811,13 +7823,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40355</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40445</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40466</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7844,7 +7856,7 @@
       <c r="I12" t="n">
         <v>0.4111111111111111</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40466</v>
       </c>
       <c r="K12" t="n">
@@ -7857,13 +7869,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40446</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7890,7 +7902,7 @@
       <c r="I13" t="n">
         <v>0.4522222222222222</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="K13" t="n">
@@ -7903,13 +7915,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40653</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7936,7 +7948,7 @@
       <c r="I14" t="n">
         <v>0.4833333333333333</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40653</v>
       </c>
       <c r="K14" t="n">
@@ -7949,13 +7961,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40635</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40745</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7982,7 +7994,7 @@
       <c r="I15" t="n">
         <v>0.5177777777777778</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40745</v>
       </c>
       <c r="K15" t="n">
@@ -7995,13 +8007,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40726</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>40842</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -8028,7 +8040,7 @@
       <c r="I16" t="n">
         <v>0.5411111111111111</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>40842</v>
       </c>
       <c r="K16" t="n">
@@ -8041,13 +8053,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>40907</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>40960</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -8074,7 +8086,7 @@
       <c r="I17" t="n">
         <v>0.5577777777777778</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>40960</v>
       </c>
       <c r="K17" t="n">
@@ -8087,13 +8099,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>40998</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41018</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8120,7 +8132,7 @@
       <c r="I18" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41018</v>
       </c>
       <c r="K18" t="n">
@@ -8133,13 +8145,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41109</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8166,7 +8178,7 @@
       <c r="I19" t="n">
         <v>0.5933333333333334</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41109</v>
       </c>
       <c r="K19" t="n">
@@ -8179,13 +8191,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41180</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41198</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8212,7 +8224,7 @@
       <c r="I20" t="n">
         <v>0.5966666666666667</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41198</v>
       </c>
       <c r="K20" t="n">
@@ -8225,13 +8237,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41181</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41271</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41324</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8258,7 +8270,7 @@
       <c r="I21" t="n">
         <v>0.5966666666666667</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41324</v>
       </c>
       <c r="K21" t="n">
@@ -8271,13 +8283,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41272</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41362</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41380</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8304,7 +8316,7 @@
       <c r="I22" t="n">
         <v>0.6033333333333334</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41380</v>
       </c>
       <c r="K22" t="n">
@@ -8317,13 +8329,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41363</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41453</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41472</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8350,7 +8362,7 @@
       <c r="I23" t="n">
         <v>0.6133333333333334</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41472</v>
       </c>
       <c r="K23" t="n">
@@ -8363,13 +8375,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41454</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41544</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41563</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8396,7 +8408,7 @@
       <c r="I24" t="n">
         <v>0.62</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41563</v>
       </c>
       <c r="K24" t="n">
@@ -8409,13 +8421,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41545</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41635</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41682</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8442,7 +8454,7 @@
       <c r="I25" t="n">
         <v>0.6166666666666667</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41682</v>
       </c>
       <c r="K25" t="n">
@@ -8455,13 +8467,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41636</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41726</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41745</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8488,7 +8500,7 @@
       <c r="I26" t="n">
         <v>0.6</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41745</v>
       </c>
       <c r="K26" t="n">
@@ -8501,13 +8513,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41727</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>41817</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>41835</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8534,7 +8546,7 @@
       <c r="I27" t="n">
         <v>0.6033333333333333</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>41835</v>
       </c>
       <c r="K27" t="n">
@@ -8547,13 +8559,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>41818</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>41908</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>41927</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8580,7 +8592,7 @@
       <c r="I28" t="n">
         <v>0.62</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>41927</v>
       </c>
       <c r="K28" t="n">
@@ -8593,13 +8605,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>41909</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>41999</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42046</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8626,7 +8638,7 @@
       <c r="I29" t="n">
         <v>0.6433333333333333</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42046</v>
       </c>
       <c r="K29" t="n">
@@ -8639,13 +8651,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42000</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42090</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42109</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8672,7 +8684,7 @@
       <c r="I30" t="n">
         <v>0.66</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42109</v>
       </c>
       <c r="K30" t="n">
@@ -8685,13 +8697,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42091</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42181</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42200</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8718,7 +8730,7 @@
       <c r="I31" t="n">
         <v>0.67</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42200</v>
       </c>
       <c r="K31" t="n">
@@ -8731,13 +8743,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42182</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42272</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42291</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8764,7 +8776,7 @@
       <c r="I32" t="n">
         <v>0.6733333333333333</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42291</v>
       </c>
       <c r="K32" t="n">
@@ -8777,13 +8789,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42273</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42363</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42410</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8810,7 +8822,7 @@
       <c r="I33" t="n">
         <v>0.67</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42410</v>
       </c>
       <c r="K33" t="n">
@@ -8823,13 +8835,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42364</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42454</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42473</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8856,7 +8868,7 @@
       <c r="I34" t="n">
         <v>0.6433333333333333</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42473</v>
       </c>
       <c r="K34" t="n">
@@ -8869,13 +8881,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42455</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42545</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42565</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8902,7 +8914,7 @@
       <c r="I35" t="n">
         <v>0.6133333333333333</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42565</v>
       </c>
       <c r="K35" t="n">
@@ -8915,13 +8927,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42546</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42636</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42655</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8948,7 +8960,7 @@
       <c r="I36" t="n">
         <v>0.6</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42655</v>
       </c>
       <c r="K36" t="n">
@@ -8961,13 +8973,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42637</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42734</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42780</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8994,7 +9006,7 @@
       <c r="I37" t="n">
         <v>0.6033333333333333</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42780</v>
       </c>
       <c r="K37" t="n">
@@ -9007,13 +9019,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>42845</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -9040,7 +9052,7 @@
       <c r="I38" t="n">
         <v>0.61</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>42845</v>
       </c>
       <c r="K38" t="n">
@@ -9053,13 +9065,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>42935</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -9086,7 +9098,7 @@
       <c r="I39" t="n">
         <v>0.6366666666666667</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>42935</v>
       </c>
       <c r="K39" t="n">
@@ -9099,13 +9111,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43026</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9132,7 +9144,7 @@
       <c r="I40" t="n">
         <v>0.6466666666666667</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43026</v>
       </c>
       <c r="K40" t="n">
@@ -9145,13 +9157,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43138</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9178,7 +9190,7 @@
       <c r="I41" t="n">
         <v>2.023333333333333</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43138</v>
       </c>
       <c r="K41" t="n">
@@ -9191,13 +9203,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43208</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9224,7 +9236,7 @@
       <c r="I42" t="n">
         <v>2.153333333333333</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43208</v>
       </c>
       <c r="K42" t="n">
@@ -9237,13 +9249,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43299</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9270,7 +9282,7 @@
       <c r="I43" t="n">
         <v>2.306666666666667</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43299</v>
       </c>
       <c r="K43" t="n">
@@ -9283,13 +9295,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43390</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9316,7 +9328,7 @@
       <c r="I44" t="n">
         <v>2.486666666666667</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43390</v>
       </c>
       <c r="K44" t="n">
@@ -9329,13 +9341,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43502</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9362,7 +9374,7 @@
       <c r="I45" t="n">
         <v>1.283333333333333</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43502</v>
       </c>
       <c r="K45" t="n">
@@ -9375,13 +9387,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43572</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9408,7 +9420,7 @@
       <c r="I46" t="n">
         <v>1.363333333333333</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43572</v>
       </c>
       <c r="K46" t="n">
@@ -9421,13 +9433,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43663</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9454,7 +9466,7 @@
       <c r="I47" t="n">
         <v>1.386666666666667</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43663</v>
       </c>
       <c r="K47" t="n">
@@ -9467,13 +9479,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43755</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9500,7 +9512,7 @@
       <c r="I48" t="n">
         <v>1.396666666666667</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43755</v>
       </c>
       <c r="K48" t="n">
@@ -9513,13 +9525,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>43873</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9546,7 +9558,7 @@
       <c r="I49" t="n">
         <v>1.39</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>43873</v>
       </c>
       <c r="K49" t="n">
@@ -9559,13 +9571,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>43944</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9592,7 +9604,7 @@
       <c r="I50" t="n">
         <v>1.383333333333334</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>43944</v>
       </c>
       <c r="K50" t="n">
@@ -9605,13 +9617,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44035</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9638,7 +9650,7 @@
       <c r="I51" t="n">
         <v>1.24</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44035</v>
       </c>
       <c r="K51" t="n">
@@ -9651,13 +9663,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44126</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9684,7 +9696,7 @@
       <c r="I52" t="n">
         <v>1.2</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44126</v>
       </c>
       <c r="K52" t="n">
@@ -9697,13 +9709,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44237</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9730,7 +9742,7 @@
       <c r="I53" t="n">
         <v>1.2</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44237</v>
       </c>
       <c r="K53" t="n">
@@ -9743,13 +9755,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44307</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9776,7 +9788,7 @@
       <c r="I54" t="n">
         <v>1.176666666666667</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44307</v>
       </c>
       <c r="K54" t="n">
@@ -9789,13 +9801,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44399</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9822,7 +9834,7 @@
       <c r="I55" t="n">
         <v>1.48</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44399</v>
       </c>
       <c r="K55" t="n">
@@ -9835,13 +9847,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44490</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9868,7 +9880,7 @@
       <c r="I56" t="n">
         <v>1.59</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44490</v>
       </c>
       <c r="K56" t="n">
@@ -9881,13 +9893,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44608</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9914,7 +9926,7 @@
       <c r="I57" t="n">
         <v>1.68</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44608</v>
       </c>
       <c r="K57" t="n">
@@ -9927,13 +9939,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44672</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9960,7 +9972,7 @@
       <c r="I58" t="n">
         <v>1.76</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44672</v>
       </c>
       <c r="K58" t="n">
@@ -9973,13 +9985,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44763</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -10006,7 +10018,7 @@
       <c r="I59" t="n">
         <v>1.78</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44763</v>
       </c>
       <c r="K59" t="n">
@@ -10019,13 +10031,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>44855</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -10052,7 +10064,7 @@
       <c r="I60" t="n">
         <v>1.87</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>44855</v>
       </c>
       <c r="K60" t="n">
@@ -10065,13 +10077,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>44972</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10098,7 +10110,7 @@
       <c r="I61" t="n">
         <v>1.95</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>44972</v>
       </c>
       <c r="K61" t="n">
@@ -10111,13 +10123,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45036</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10144,7 +10156,7 @@
       <c r="I62" t="n">
         <v>2.04</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45036</v>
       </c>
       <c r="K62" t="n">
@@ -10157,13 +10169,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45127</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10190,7 +10202,7 @@
       <c r="I63" t="n">
         <v>1.99</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45127</v>
       </c>
       <c r="K63" t="n">
@@ -10203,13 +10215,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45219</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10236,7 +10248,7 @@
       <c r="I64" t="n">
         <v>1.89</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45219</v>
       </c>
       <c r="K64" t="n">
@@ -10249,13 +10261,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45336</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10282,7 +10294,7 @@
       <c r="I65" t="n">
         <v>1.85</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45336</v>
       </c>
       <c r="K65" t="n">
@@ -10295,13 +10307,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45400</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10328,7 +10340,7 @@
       <c r="I66" t="n">
         <v>1.83</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45400</v>
       </c>
       <c r="K66" t="n">
@@ -10341,13 +10353,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45509</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10374,7 +10386,7 @@
       <c r="I67" t="n">
         <v>1.83</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45509</v>
       </c>
       <c r="K67" t="n">
@@ -10387,13 +10399,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45582</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10420,7 +10432,7 @@
       <c r="I68" t="n">
         <v>1.87</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45582</v>
       </c>
       <c r="K68" t="n">
@@ -10433,13 +10445,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45715</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10466,7 +10478,7 @@
       <c r="I69" t="n">
         <v>1.79</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45715</v>
       </c>
       <c r="K69" t="n">
@@ -10479,13 +10491,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45763</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10512,7 +10524,7 @@
       <c r="I70" t="n">
         <v>1.67</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45763</v>
       </c>
       <c r="K70" t="n">
@@ -10525,13 +10537,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>45861</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10558,7 +10570,7 @@
       <c r="I71" t="n">
         <v>1.62</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>45861</v>
       </c>
       <c r="K71" t="n">
@@ -10571,13 +10583,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>45946</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10604,7 +10616,7 @@
       <c r="I72" t="n">
         <v>1.53</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>45946</v>
       </c>
       <c r="K72" t="n">
@@ -10617,13 +10629,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10650,7 +10662,7 @@
       <c r="I73" t="n">
         <v>1.54</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="K73" t="n">
@@ -10663,13 +10675,13 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B74" s="1" t="n">
+      <c r="B74" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C74" s="1" t="n">
+      <c r="C74" s="2" t="n">
         <v>46134</v>
       </c>
       <c r="D74" t="inlineStr">
@@ -10696,7 +10708,7 @@
       <c r="I74" t="n">
         <v>1.63</v>
       </c>
-      <c r="J74" s="1" t="n">
+      <c r="J74" s="2" t="n">
         <v>46134</v>
       </c>
       <c r="K74" t="n">
@@ -10709,13 +10721,13 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B75" s="1" t="n">
+      <c r="B75" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C75" s="1" t="n">
+      <c r="C75" s="2" t="n">
         <v>46225</v>
       </c>
       <c r="D75" t="inlineStr">
@@ -10742,7 +10754,7 @@
       <c r="I75" t="n">
         <v>1.73</v>
       </c>
-      <c r="J75" s="1" t="n">
+      <c r="J75" s="2" t="n">
         <v>46225</v>
       </c>
       <c r="K75" t="n">
@@ -10779,52 +10791,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39899</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39918</v>
       </c>
       <c r="C2" t="n">
@@ -10853,10 +10865,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39990</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40009</v>
       </c>
       <c r="C3" t="n">
@@ -10885,10 +10897,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40081</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40106</v>
       </c>
       <c r="C4" t="n">
@@ -10917,10 +10929,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40214</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40228</v>
       </c>
       <c r="C5" t="n">
@@ -10949,10 +10961,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40263</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40287</v>
       </c>
       <c r="C6" t="n">
@@ -10981,10 +10993,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40354</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40374</v>
       </c>
       <c r="C7" t="n">
@@ -11013,10 +11025,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40445</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40466</v>
       </c>
       <c r="C8" t="n">
@@ -11045,10 +11057,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>39808</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="C9" t="n">
@@ -11077,10 +11089,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>39444</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="C10" t="n">
@@ -11109,10 +11121,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40172</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="C11" t="n">
@@ -11141,10 +11153,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="C12" t="n">
@@ -11173,10 +11185,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40745</v>
       </c>
       <c r="C13" t="n">
@@ -11205,10 +11217,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40842</v>
       </c>
       <c r="C14" t="n">
@@ -11237,10 +11249,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40935</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40960</v>
       </c>
       <c r="C15" t="n">
@@ -11269,10 +11281,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40998</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41018</v>
       </c>
       <c r="C16" t="n">
@@ -11301,10 +11313,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41109</v>
       </c>
       <c r="C17" t="n">
@@ -11333,10 +11345,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41180</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41198</v>
       </c>
       <c r="C18" t="n">
@@ -11365,10 +11377,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41299</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41324</v>
       </c>
       <c r="C19" t="n">
@@ -11397,10 +11409,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41362</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41380</v>
       </c>
       <c r="C20" t="n">
@@ -11429,10 +11441,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41453</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41472</v>
       </c>
       <c r="C21" t="n">
@@ -11461,10 +11473,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41544</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41563</v>
       </c>
       <c r="C22" t="n">
@@ -11493,10 +11505,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41663</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41682</v>
       </c>
       <c r="C23" t="n">
@@ -11525,10 +11537,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41726</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41745</v>
       </c>
       <c r="C24" t="n">
@@ -11557,10 +11569,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41817</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41835</v>
       </c>
       <c r="C25" t="n">
@@ -11589,10 +11601,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41908</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41927</v>
       </c>
       <c r="C26" t="n">
@@ -11621,10 +11633,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42027</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42046</v>
       </c>
       <c r="C27" t="n">
@@ -11653,10 +11665,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42090</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42109</v>
       </c>
       <c r="C28" t="n">
@@ -11685,10 +11697,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42181</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42200</v>
       </c>
       <c r="C29" t="n">
@@ -11717,10 +11729,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42272</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42291</v>
       </c>
       <c r="C30" t="n">
@@ -11749,10 +11761,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42391</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42410</v>
       </c>
       <c r="C31" t="n">
@@ -11781,10 +11793,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42454</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42473</v>
       </c>
       <c r="C32" t="n">
@@ -11813,10 +11825,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42545</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42565</v>
       </c>
       <c r="C33" t="n">
@@ -11845,10 +11857,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42636</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42655</v>
       </c>
       <c r="C34" t="n">
@@ -11877,10 +11889,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42762</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42780</v>
       </c>
       <c r="C35" t="n">
@@ -11909,10 +11921,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42845</v>
       </c>
       <c r="C36" t="n">
@@ -11941,10 +11953,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42935</v>
       </c>
       <c r="C37" t="n">
@@ -11973,10 +11985,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43026</v>
       </c>
       <c r="C38" t="n">
@@ -12005,10 +12017,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43138</v>
       </c>
       <c r="C39" t="n">
@@ -12037,10 +12049,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43208</v>
       </c>
       <c r="C40" t="n">
@@ -12069,10 +12081,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43299</v>
       </c>
       <c r="C41" t="n">
@@ -12101,10 +12113,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43390</v>
       </c>
       <c r="C42" t="n">
@@ -12133,10 +12145,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43502</v>
       </c>
       <c r="C43" t="n">
@@ -12165,10 +12177,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43572</v>
       </c>
       <c r="C44" t="n">
@@ -12197,10 +12209,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43663</v>
       </c>
       <c r="C45" t="n">
@@ -12229,10 +12241,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43755</v>
       </c>
       <c r="C46" t="n">
@@ -12261,10 +12273,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43873</v>
       </c>
       <c r="C47" t="n">
@@ -12293,10 +12305,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43944</v>
       </c>
       <c r="C48" t="n">
@@ -12325,10 +12337,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44035</v>
       </c>
       <c r="C49" t="n">
@@ -12357,10 +12369,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44126</v>
       </c>
       <c r="C50" t="n">
@@ -12389,10 +12401,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44237</v>
       </c>
       <c r="C51" t="n">
@@ -12421,10 +12433,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44307</v>
       </c>
       <c r="C52" t="n">
@@ -12453,10 +12465,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44399</v>
       </c>
       <c r="C53" t="n">
@@ -12485,10 +12497,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44490</v>
       </c>
       <c r="C54" t="n">
@@ -12517,10 +12529,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44608</v>
       </c>
       <c r="C55" t="n">
@@ -12549,10 +12561,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44672</v>
       </c>
       <c r="C56" t="n">
@@ -12581,10 +12593,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44763</v>
       </c>
       <c r="C57" t="n">
@@ -12613,10 +12625,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44855</v>
       </c>
       <c r="C58" t="n">
@@ -12645,10 +12657,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44972</v>
       </c>
       <c r="C59" t="n">
@@ -12677,10 +12689,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45036</v>
       </c>
       <c r="C60" t="n">
@@ -12709,10 +12721,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45127</v>
       </c>
       <c r="C61" t="n">
@@ -12741,10 +12753,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45219</v>
       </c>
       <c r="C62" t="n">
@@ -12773,10 +12785,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45322</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45336</v>
       </c>
       <c r="C63" t="n">
@@ -12805,10 +12817,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45400</v>
       </c>
       <c r="C64" t="n">
@@ -12837,10 +12849,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45509</v>
       </c>
       <c r="C65" t="n">
@@ -12869,10 +12881,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45582</v>
       </c>
       <c r="C66" t="n">
@@ -12901,10 +12913,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45715</v>
       </c>
       <c r="C67" t="n">
@@ -12933,10 +12945,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45763</v>
       </c>
       <c r="C68" t="n">
@@ -12965,10 +12977,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45861</v>
       </c>
       <c r="C69" t="n">
@@ -12997,10 +13009,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45946</v>
       </c>
       <c r="C70" t="n">
@@ -13029,10 +13041,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="C71" t="n">
@@ -13061,10 +13073,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46134</v>
       </c>
       <c r="C72" t="n">
@@ -13093,10 +13105,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46225</v>
       </c>
       <c r="C73" t="n">
@@ -13143,12 +13155,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/CSX.xlsx
+++ b/salidas/empresas/CSX.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>2.089351177215576</v>
+        <v>2.089351892471313</v>
       </c>
       <c r="C2" t="n">
         <v>2.973889112472534</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>2.166719198226929</v>
+        <v>2.166718482971191</v>
       </c>
       <c r="C3" t="n">
         <v>3.076667070388794</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>2.33965015411377</v>
+        <v>2.339649438858032</v>
       </c>
       <c r="C4" t="n">
         <v>3.322221994400024</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>2.679643630981445</v>
+        <v>2.679642200469971</v>
       </c>
       <c r="C5" t="n">
         <v>3.805000066757202</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>2.623332262039185</v>
+        <v>2.623332023620605</v>
       </c>
       <c r="C6" t="n">
         <v>3.717777967453003</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>2.761318922042847</v>
+        <v>2.761318445205688</v>
       </c>
       <c r="C7" t="n">
         <v>3.913332939147949</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>2.378716945648193</v>
+        <v>2.378718137741089</v>
       </c>
       <c r="C8" t="n">
         <v>3.371110916137695</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>2.582425117492676</v>
+        <v>2.582425355911255</v>
       </c>
       <c r="C10" t="n">
         <v>3.647778034210205</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>2.805819988250732</v>
+        <v>2.80582070350647</v>
       </c>
       <c r="C11" t="n">
         <v>3.963332891464233</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>2.715734720230103</v>
+        <v>2.715734243392944</v>
       </c>
       <c r="C13" t="n">
         <v>3.825556039810181</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>2.901882886886597</v>
+        <v>2.901883363723755</v>
       </c>
       <c r="C14" t="n">
         <v>4.087778091430664</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>2.976402282714844</v>
+        <v>2.976402997970581</v>
       </c>
       <c r="C15" t="n">
         <v>4.179999828338623</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>3.168658494949341</v>
+        <v>3.16865873336792</v>
       </c>
       <c r="C16" t="n">
         <v>4.449999809265137</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>3.415505886077881</v>
+        <v>3.415504693984985</v>
       </c>
       <c r="C17" t="n">
         <v>4.796667098999023</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>3.604766368865967</v>
+        <v>3.604768037796021</v>
       </c>
       <c r="C18" t="n">
         <v>5.04888916015625</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>3.57620644569397</v>
+        <v>3.576206922531128</v>
       </c>
       <c r="C19" t="n">
         <v>5.008889198303223</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>3.761048078536987</v>
+        <v>3.76104736328125</v>
       </c>
       <c r="C20" t="n">
         <v>5.267777919769287</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>3.264498472213745</v>
+        <v>3.264497995376587</v>
       </c>
       <c r="C21" t="n">
         <v>4.555555820465088</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>3.402243614196777</v>
+        <v>3.402244329452515</v>
       </c>
       <c r="C22" t="n">
         <v>4.747777938842773</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>3.564671993255615</v>
+        <v>3.564671754837036</v>
       </c>
       <c r="C23" t="n">
         <v>4.974443912506104</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>3.356348991394043</v>
+        <v>3.35634708404541</v>
       </c>
       <c r="C24" t="n">
         <v>4.666666984558105</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>3.514578104019165</v>
+        <v>3.514577388763428</v>
       </c>
       <c r="C25" t="n">
         <v>4.886666774749756</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>3.87258768081665</v>
+        <v>3.872586011886597</v>
       </c>
       <c r="C26" t="n">
         <v>5.384444236755371</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>3.888444900512695</v>
+        <v>3.888445854187012</v>
       </c>
       <c r="C27" t="n">
         <v>5.391110897064209</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>4.493510723114014</v>
+        <v>4.493510246276855</v>
       </c>
       <c r="C28" t="n">
         <v>6.230000019073486</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>5.044880867004395</v>
+        <v>5.044882297515869</v>
       </c>
       <c r="C29" t="n">
         <v>6.994443893432617</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>5.549366474151611</v>
+        <v>5.54936695098877</v>
       </c>
       <c r="C30" t="n">
         <v>7.673333168029785</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>5.047142028808594</v>
+        <v>5.04714298248291</v>
       </c>
       <c r="C31" t="n">
         <v>6.978888988494873</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>5.430440902709961</v>
+        <v>5.430439472198486</v>
       </c>
       <c r="C32" t="n">
         <v>7.508889198303223</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>5.215509414672852</v>
+        <v>5.215508460998535</v>
       </c>
       <c r="C33" t="n">
         <v>7.186666965484619</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>4.400283813476562</v>
+        <v>4.400282382965088</v>
       </c>
       <c r="C34" t="n">
         <v>6.063333034515381</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>3.686656951904297</v>
+        <v>3.686659574508667</v>
       </c>
       <c r="C35" t="n">
         <v>5.079999923706055</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>3.021026849746704</v>
+        <v>3.021027088165283</v>
       </c>
       <c r="C36" t="n">
         <v>4.137777805328369</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>2.349327564239502</v>
+        <v>2.349327325820923</v>
       </c>
       <c r="C38" t="n">
         <v>3.217777967453003</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>2.018735647201538</v>
+        <v>2.018734455108643</v>
       </c>
       <c r="C39" t="n">
         <v>2.74222207069397</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>2.420355558395386</v>
+        <v>2.42035436630249</v>
       </c>
       <c r="C41" t="n">
         <v>3.287777900695801</v>
@@ -1264,7 +1264,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>2.617142200469971</v>
+        <v>2.617142677307129</v>
       </c>
       <c r="C42" t="n">
         <v>3.528888940811157</v>
@@ -1289,7 +1289,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>2.853641510009766</v>
+        <v>2.853641271591187</v>
       </c>
       <c r="C43" t="n">
         <v>3.847778081893921</v>
@@ -1314,7 +1314,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>3.306037664413452</v>
+        <v>3.306037902832031</v>
       </c>
       <c r="C44" t="n">
         <v>4.457777976989746</v>
@@ -1339,7 +1339,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>3.520146131515503</v>
+        <v>3.520146608352661</v>
       </c>
       <c r="C45" t="n">
         <v>4.722221851348877</v>
@@ -1364,7 +1364,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>3.467138528823853</v>
+        <v>3.467136383056641</v>
       </c>
       <c r="C46" t="n">
         <v>4.651111125946045</v>
@@ -1389,7 +1389,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>3.493643522262573</v>
+        <v>3.493640899658203</v>
       </c>
       <c r="C47" t="n">
         <v>4.686666965484619</v>
@@ -1414,7 +1414,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>3.950731039047241</v>
+        <v>3.950733423233032</v>
       </c>
       <c r="C48" t="n">
         <v>5.275556087493896</v>
@@ -1439,7 +1439,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>4.034773826599121</v>
+        <v>4.034772872924805</v>
       </c>
       <c r="C49" t="n">
         <v>5.387777805328369</v>
@@ -1489,7 +1489,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>3.969337940216064</v>
+        <v>3.969337701797485</v>
       </c>
       <c r="C51" t="n">
         <v>5.273333072662354</v>
@@ -1518,7 +1518,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>4.257045269012451</v>
+        <v>4.25704288482666</v>
       </c>
       <c r="C52" t="n">
         <v>5.655556201934814</v>
@@ -1547,7 +1547,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>4.687766551971436</v>
+        <v>4.687768936157227</v>
       </c>
       <c r="C53" t="n">
         <v>6.22777795791626</v>
@@ -1576,7 +1576,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>4.390827178955078</v>
+        <v>4.390828609466553</v>
       </c>
       <c r="C54" t="n">
         <v>5.805555820465088</v>
@@ -1605,7 +1605,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>4.170654773712158</v>
+        <v>4.170655250549316</v>
       </c>
       <c r="C55" t="n">
         <v>5.514443874359131</v>
@@ -1663,7 +1663,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>4.213371753692627</v>
+        <v>4.213372707366943</v>
       </c>
       <c r="C57" t="n">
         <v>5.543333053588867</v>
@@ -1721,7 +1721,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>5.189651489257812</v>
+        <v>5.18964958190918</v>
       </c>
       <c r="C59" t="n">
         <v>6.827777862548828</v>
@@ -1750,7 +1750,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>5.157262325286865</v>
+        <v>5.157262802124023</v>
       </c>
       <c r="C60" t="n">
         <v>6.756667137145996</v>
@@ -1808,7 +1808,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>5.987547874450684</v>
+        <v>5.987548351287842</v>
       </c>
       <c r="C62" t="n">
         <v>7.844443798065186</v>
@@ -1837,7 +1837,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>6.354968070983887</v>
+        <v>6.354969501495361</v>
       </c>
       <c r="C63" t="n">
         <v>8.29555606842041</v>
@@ -1866,7 +1866,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>6.690336227416992</v>
+        <v>6.69033670425415</v>
       </c>
       <c r="C64" t="n">
         <v>8.733332633972168</v>
@@ -1895,7 +1895,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>6.698001384735107</v>
+        <v>6.698000431060791</v>
       </c>
       <c r="C65" t="n">
         <v>8.743332862854004</v>
@@ -1924,7 +1924,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>6.781764507293701</v>
+        <v>6.781765937805176</v>
       </c>
       <c r="C66" t="n">
         <v>8.811111450195312</v>
@@ -1953,7 +1953,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>6.72703218460083</v>
+        <v>6.727031707763672</v>
       </c>
       <c r="C67" t="n">
         <v>8.739999771118164</v>
@@ -1982,7 +1982,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>6.303707122802734</v>
+        <v>6.303705215454102</v>
       </c>
       <c r="C68" t="n">
         <v>8.189999580383301</v>
@@ -2011,7 +2011,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>5.660619258880615</v>
+        <v>5.660619735717773</v>
       </c>
       <c r="C69" t="n">
         <v>7.313333034515381</v>
@@ -2040,7 +2040,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>4.816943645477295</v>
+        <v>4.816943168640137</v>
       </c>
       <c r="C70" t="n">
         <v>6.22333288192749</v>
@@ -2069,7 +2069,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>5.730279922485352</v>
+        <v>5.730278968811035</v>
       </c>
       <c r="C71" t="n">
         <v>7.403333187103271</v>
@@ -2098,7 +2098,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>5.635087013244629</v>
+        <v>5.635087966918945</v>
       </c>
       <c r="C72" t="n">
         <v>7.236667156219482</v>
@@ -2127,7 +2127,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>5.466372966766357</v>
+        <v>5.466372489929199</v>
       </c>
       <c r="C73" t="n">
         <v>7.019999980926514</v>
@@ -2185,7 +2185,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>5.483774662017822</v>
+        <v>5.483776092529297</v>
       </c>
       <c r="C75" t="n">
         <v>7.00333309173584</v>
@@ -2214,7 +2214,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>5.616890430450439</v>
+        <v>5.616889476776123</v>
       </c>
       <c r="C76" t="n">
         <v>7.173333168029785</v>
@@ -2243,7 +2243,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>5.81786584854126</v>
+        <v>5.817864418029785</v>
       </c>
       <c r="C77" t="n">
         <v>7.429999828338623</v>
@@ -2272,7 +2272,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>5.488409996032715</v>
+        <v>5.488411426544189</v>
       </c>
       <c r="C78" t="n">
         <v>6.963333129882812</v>
@@ -2301,7 +2301,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>5.87462329864502</v>
+        <v>5.874622344970703</v>
       </c>
       <c r="C79" t="n">
         <v>7.453332901000977</v>
@@ -2330,7 +2330,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>6.027005672454834</v>
+        <v>6.027004241943359</v>
       </c>
       <c r="C80" t="n">
         <v>7.646667003631592</v>
@@ -2359,7 +2359,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>5.937515258789062</v>
+        <v>5.937516212463379</v>
       </c>
       <c r="C81" t="n">
         <v>7.486667156219482</v>
@@ -2388,7 +2388,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>5.485462665557861</v>
+        <v>5.485459327697754</v>
       </c>
       <c r="C82" t="n">
         <v>6.916666984558105</v>
@@ -2417,7 +2417,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>5.411438941955566</v>
+        <v>5.411439418792725</v>
       </c>
       <c r="C83" t="n">
         <v>6.823332786560059</v>
@@ -2446,7 +2446,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>5.260548114776611</v>
+        <v>5.260550022125244</v>
       </c>
       <c r="C84" t="n">
         <v>6.586667060852051</v>
@@ -2504,7 +2504,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>5.864873886108398</v>
+        <v>5.86487340927124</v>
       </c>
       <c r="C86" t="n">
         <v>7.343332767486572</v>
@@ -2533,7 +2533,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>6.145859718322754</v>
+        <v>6.145859241485596</v>
       </c>
       <c r="C87" t="n">
         <v>7.646667003631592</v>
@@ -2562,7 +2562,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>6.598626613616943</v>
+        <v>6.598629474639893</v>
       </c>
       <c r="C88" t="n">
         <v>8.210000038146973</v>
@@ -2591,7 +2591,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>6.587911128997803</v>
+        <v>6.587910652160645</v>
       </c>
       <c r="C89" t="n">
         <v>8.196666717529297</v>
@@ -2620,7 +2620,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>6.794297218322754</v>
+        <v>6.794299125671387</v>
       </c>
       <c r="C90" t="n">
         <v>8.403332710266113</v>
@@ -2649,7 +2649,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>6.249893188476562</v>
+        <v>6.24989128112793</v>
       </c>
       <c r="C91" t="n">
         <v>7.730000019073486</v>
@@ -2678,7 +2678,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>6.68649435043335</v>
+        <v>6.686495780944824</v>
       </c>
       <c r="C92" t="n">
         <v>8.270000457763672</v>
@@ -2707,7 +2707,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>6.672937870025635</v>
+        <v>6.672935962677002</v>
       </c>
       <c r="C93" t="n">
         <v>8.203332901000977</v>
@@ -2736,7 +2736,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>6.979333400726318</v>
+        <v>6.979335784912109</v>
       </c>
       <c r="C94" t="n">
         <v>8.579999923706055</v>
@@ -2765,7 +2765,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>7.066100597381592</v>
+        <v>7.06610107421875</v>
       </c>
       <c r="C95" t="n">
         <v>8.686667442321777</v>
@@ -2794,7 +2794,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>7.434889793395996</v>
+        <v>7.434891700744629</v>
       </c>
       <c r="C96" t="n">
         <v>9.090000152587891</v>
@@ -2823,7 +2823,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>7.843854427337646</v>
+        <v>7.843852043151855</v>
       </c>
       <c r="C97" t="n">
         <v>9.590000152587891</v>
@@ -2852,7 +2852,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>7.33674144744873</v>
+        <v>7.336743354797363</v>
       </c>
       <c r="C98" t="n">
         <v>8.970000267028809</v>
@@ -2881,7 +2881,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>7.596576690673828</v>
+        <v>7.596578121185303</v>
       </c>
       <c r="C99" t="n">
         <v>9.236666679382324</v>
@@ -2939,7 +2939,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>7.736391544342041</v>
+        <v>7.736390113830566</v>
       </c>
       <c r="C101" t="n">
         <v>9.40666675567627</v>
@@ -2968,7 +2968,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>8.103913307189941</v>
+        <v>8.103912353515625</v>
       </c>
       <c r="C102" t="n">
         <v>9.800000190734863</v>
@@ -2997,7 +2997,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>8.49256706237793</v>
+        <v>8.492569923400879</v>
       </c>
       <c r="C103" t="n">
         <v>10.27000045776367</v>
@@ -3026,7 +3026,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>8.247247695922852</v>
+        <v>8.247244834899902</v>
       </c>
       <c r="C104" t="n">
         <v>9.973333358764648</v>
@@ -3055,7 +3055,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>8.564579010009766</v>
+        <v>8.564580917358398</v>
       </c>
       <c r="C105" t="n">
         <v>10.3033332824707</v>
@@ -3084,7 +3084,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>8.883225440979004</v>
+        <v>8.88322639465332</v>
       </c>
       <c r="C106" t="n">
         <v>10.68666744232178</v>
@@ -3113,7 +3113,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>9.872403144836426</v>
+        <v>9.872404098510742</v>
       </c>
       <c r="C107" t="n">
         <v>11.87666702270508</v>
@@ -3171,7 +3171,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>10.08123683929443</v>
+        <v>10.08123111724854</v>
       </c>
       <c r="C109" t="n">
         <v>12.07666683197021</v>
@@ -3200,7 +3200,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>9.265945434570312</v>
+        <v>9.265942573547363</v>
       </c>
       <c r="C110" t="n">
         <v>11.10000038146973</v>
@@ -3229,7 +3229,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>9.590121269226074</v>
+        <v>9.590124130249023</v>
       </c>
       <c r="C111" t="n">
         <v>11.43666744232178</v>
@@ -3258,7 +3258,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>9.257497787475586</v>
+        <v>9.257495880126953</v>
       </c>
       <c r="C112" t="n">
         <v>11.03999996185303</v>
@@ -3316,7 +3316,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>9.575386047363281</v>
+        <v>9.57538890838623</v>
       </c>
       <c r="C114" t="n">
         <v>11.35999965667725</v>
@@ -3345,7 +3345,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>9.173603057861328</v>
+        <v>9.173601150512695</v>
       </c>
       <c r="C115" t="n">
         <v>10.88333320617676</v>
@@ -3374,7 +3374,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>8.788678169250488</v>
+        <v>8.788676261901855</v>
       </c>
       <c r="C116" t="n">
         <v>10.42666721343994</v>
@@ -3403,7 +3403,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>7.745772838592529</v>
+        <v>7.745773792266846</v>
       </c>
       <c r="C117" t="n">
         <v>9.126667022705078</v>
@@ -3432,7 +3432,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>7.609984874725342</v>
+        <v>7.609981536865234</v>
       </c>
       <c r="C118" t="n">
         <v>8.966667175292969</v>
@@ -3461,7 +3461,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>7.635444164276123</v>
+        <v>7.635443687438965</v>
       </c>
       <c r="C119" t="n">
         <v>8.99666690826416</v>
@@ -3490,7 +3490,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>8.093002319335938</v>
+        <v>8.093000411987305</v>
       </c>
       <c r="C120" t="n">
         <v>9.476667404174805</v>
@@ -3519,7 +3519,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>7.387032985687256</v>
+        <v>7.387032508850098</v>
       </c>
       <c r="C121" t="n">
         <v>8.649999618530273</v>
@@ -3548,7 +3548,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>6.552965641021729</v>
+        <v>6.55296802520752</v>
       </c>
       <c r="C122" t="n">
         <v>7.673333168029785</v>
@@ -3577,7 +3577,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>6.922671794891357</v>
+        <v>6.922672748565674</v>
       </c>
       <c r="C123" t="n">
         <v>8.046667098999023</v>
@@ -3635,7 +3635,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>7.820268630981445</v>
+        <v>7.820265293121338</v>
       </c>
       <c r="C125" t="n">
         <v>9.090000152587891</v>
@@ -3664,7 +3664,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>7.632567882537842</v>
+        <v>7.632567405700684</v>
       </c>
       <c r="C126" t="n">
         <v>8.810000419616699</v>
@@ -3693,7 +3693,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>7.531491279602051</v>
+        <v>7.531492710113525</v>
       </c>
       <c r="C127" t="n">
         <v>8.693332672119141</v>
@@ -3722,7 +3722,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>8.181260108947754</v>
+        <v>8.181259155273438</v>
       </c>
       <c r="C128" t="n">
         <v>9.443332672119141</v>
@@ -3751,7 +3751,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>8.219301223754883</v>
+        <v>8.219303131103516</v>
       </c>
       <c r="C129" t="n">
         <v>9.426667213439941</v>
@@ -3780,7 +3780,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>8.864521980285645</v>
+        <v>8.864522933959961</v>
       </c>
       <c r="C130" t="n">
         <v>10.16666698455811</v>
@@ -3809,7 +3809,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>8.867426872253418</v>
+        <v>8.867425918579102</v>
       </c>
       <c r="C131" t="n">
         <v>10.17000007629395</v>
@@ -3838,7 +3838,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>10.46132850646973</v>
+        <v>10.46132946014404</v>
       </c>
       <c r="C132" t="n">
         <v>11.93666744232178</v>
@@ -3867,7 +3867,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>10.49638748168945</v>
+        <v>10.49639415740967</v>
       </c>
       <c r="C133" t="n">
         <v>11.9766674041748</v>
@@ -3925,7 +3925,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>14.23954582214355</v>
+        <v>14.23954486846924</v>
       </c>
       <c r="C135" t="n">
         <v>16.18666648864746</v>
@@ -3954,7 +3954,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>13.65013885498047</v>
+        <v>13.65013694763184</v>
       </c>
       <c r="C136" t="n">
         <v>15.51666736602783</v>
@@ -3983,7 +3983,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>14.90812492370605</v>
+        <v>14.90812015533447</v>
       </c>
       <c r="C137" t="n">
         <v>16.9466667175293</v>
@@ -4012,7 +4012,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>15.94387722015381</v>
+        <v>15.94388198852539</v>
       </c>
       <c r="C138" t="n">
         <v>18.05666732788086</v>
@@ -4041,7 +4041,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>16.05866813659668</v>
+        <v>16.05866622924805</v>
       </c>
       <c r="C139" t="n">
         <v>18.18666648864746</v>
@@ -4070,7 +4070,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>14.52226638793945</v>
+        <v>14.52226161956787</v>
       </c>
       <c r="C140" t="n">
         <v>16.4466667175293</v>
@@ -4099,7 +4099,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>14.83532905578613</v>
+        <v>14.83533000946045</v>
       </c>
       <c r="C141" t="n">
         <v>16.73333358764648</v>
@@ -4128,7 +4128,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>16.03515815734863</v>
+        <v>16.03515625</v>
       </c>
       <c r="C142" t="n">
         <v>18.08666610717773</v>
@@ -4157,7 +4157,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>14.90329837799072</v>
+        <v>14.90329647064209</v>
       </c>
       <c r="C143" t="n">
         <v>16.80999946594238</v>
@@ -4215,7 +4215,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>16.31941795349121</v>
+        <v>16.31941413879395</v>
       </c>
       <c r="C145" t="n">
         <v>18.33666610717773</v>
@@ -4244,7 +4244,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>16.84154319763184</v>
+        <v>16.84153747558594</v>
       </c>
       <c r="C146" t="n">
         <v>18.92333221435547</v>
@@ -4273,7 +4273,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>16.00058364868164</v>
+        <v>16.00057983398438</v>
       </c>
       <c r="C147" t="n">
         <v>17.90666770935059</v>
@@ -4302,7 +4302,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>16.59330558776855</v>
+        <v>16.59330749511719</v>
       </c>
       <c r="C148" t="n">
         <v>18.56999969482422</v>
@@ -4331,7 +4331,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>17.68939971923828</v>
+        <v>17.68939781188965</v>
       </c>
       <c r="C149" t="n">
         <v>19.79666709899902</v>
@@ -4418,7 +4418,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>21.12451362609863</v>
+        <v>21.12450981140137</v>
       </c>
       <c r="C152" t="n">
         <v>23.55999946594238</v>
@@ -4447,7 +4447,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>22.22996139526367</v>
+        <v>22.22995567321777</v>
       </c>
       <c r="C153" t="n">
         <v>24.71999931335449</v>
@@ -4476,7 +4476,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>22.19698143005371</v>
+        <v>22.19698715209961</v>
       </c>
       <c r="C154" t="n">
         <v>24.6833324432373</v>
@@ -4505,7 +4505,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>20.6412467956543</v>
+        <v>20.64124298095703</v>
       </c>
       <c r="C155" t="n">
         <v>22.95333290100098</v>
@@ -4534,7 +4534,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>21.83736228942871</v>
+        <v>21.83736801147461</v>
       </c>
       <c r="C156" t="n">
         <v>24.20999908447266</v>
@@ -4563,7 +4563,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>18.68037033081055</v>
+        <v>18.68036651611328</v>
       </c>
       <c r="C157" t="n">
         <v>20.70999908447266</v>
@@ -4621,7 +4621,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>21.92169952392578</v>
+        <v>21.92170333862305</v>
       </c>
       <c r="C159" t="n">
         <v>24.22333335876465</v>
@@ -4650,7 +4650,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>22.57027435302734</v>
+        <v>22.57027053833008</v>
       </c>
       <c r="C160" t="n">
         <v>24.94000053405762</v>
@@ -4679,7 +4679,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>24.02126312255859</v>
+        <v>24.02126693725586</v>
       </c>
       <c r="C161" t="n">
         <v>26.54333305358887</v>
@@ -4708,7 +4708,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>22.5378360748291</v>
+        <v>22.537841796875</v>
       </c>
       <c r="C162" t="n">
         <v>24.82333374023438</v>
@@ -4737,7 +4737,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>23.41550064086914</v>
+        <v>23.41550636291504</v>
       </c>
       <c r="C163" t="n">
         <v>25.79000091552734</v>
@@ -4824,7 +4824,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>21.04132461547852</v>
+        <v>21.04131698608398</v>
       </c>
       <c r="C166" t="n">
         <v>23.09000015258789</v>
@@ -4853,7 +4853,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>21.3450756072998</v>
+        <v>21.34507942199707</v>
       </c>
       <c r="C167" t="n">
         <v>23.42333221435547</v>
@@ -4882,7 +4882,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>21.80357551574707</v>
+        <v>21.8035774230957</v>
       </c>
       <c r="C168" t="n">
         <v>23.84666633605957</v>
@@ -4911,7 +4911,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>22.05349540710449</v>
+        <v>22.05349731445312</v>
       </c>
       <c r="C169" t="n">
         <v>24.1200008392334</v>
@@ -4940,7 +4940,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>23.26649475097656</v>
+        <v>23.2664966583252</v>
       </c>
       <c r="C170" t="n">
         <v>25.4466667175293</v>
@@ -4969,7 +4969,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>21.54576301574707</v>
+        <v>21.5457592010498</v>
       </c>
       <c r="C171" t="n">
         <v>23.48333358764648</v>
@@ -4998,7 +4998,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>17.52408981323242</v>
+        <v>17.52409362792969</v>
       </c>
       <c r="C172" t="n">
         <v>19.10000038146973</v>
@@ -5027,7 +5027,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>20.25515174865723</v>
+        <v>20.25515747070312</v>
       </c>
       <c r="C173" t="n">
         <v>22.07666778564453</v>
@@ -5056,7 +5056,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>21.96895980834961</v>
+        <v>21.96895027160645</v>
       </c>
       <c r="C174" t="n">
         <v>23.86000061035156</v>
@@ -5114,7 +5114,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>21.89529991149902</v>
+        <v>21.89529800415039</v>
       </c>
       <c r="C176" t="n">
         <v>23.78000068664551</v>
@@ -5143,7 +5143,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>23.54705810546875</v>
+        <v>23.54705429077148</v>
       </c>
       <c r="C177" t="n">
         <v>25.48666763305664</v>
@@ -5172,7 +5172,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>23.9196949005127</v>
+        <v>23.91969108581543</v>
       </c>
       <c r="C178" t="n">
         <v>25.88999938964844</v>
@@ -5201,7 +5201,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>24.31081199645996</v>
+        <v>24.31081390380859</v>
       </c>
       <c r="C179" t="n">
         <v>26.31333351135254</v>
@@ -5230,7 +5230,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>27.81070327758789</v>
+        <v>27.81070518493652</v>
       </c>
       <c r="C180" t="n">
         <v>30.01666641235352</v>
@@ -5259,7 +5259,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>28.02688598632812</v>
+        <v>28.02688789367676</v>
       </c>
       <c r="C181" t="n">
         <v>30.25</v>
@@ -5288,7 +5288,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>26.48579025268555</v>
+        <v>26.48579216003418</v>
       </c>
       <c r="C182" t="n">
         <v>28.58666610717773</v>
@@ -5317,7 +5317,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>28.35899925231934</v>
+        <v>28.35900497436523</v>
       </c>
       <c r="C183" t="n">
         <v>30.51666641235352</v>
@@ -5346,7 +5346,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>29.86755752563477</v>
+        <v>29.8675594329834</v>
       </c>
       <c r="C184" t="n">
         <v>32.13999938964844</v>
@@ -5375,7 +5375,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>31.20883941650391</v>
+        <v>31.20883750915527</v>
       </c>
       <c r="C185" t="n">
         <v>33.58333206176758</v>
@@ -5404,7 +5404,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>31.10038185119629</v>
+        <v>31.10038375854492</v>
       </c>
       <c r="C186" t="n">
         <v>33.37333297729492</v>
@@ -5433,7 +5433,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>29.89513969421387</v>
+        <v>29.8951358795166</v>
       </c>
       <c r="C187" t="n">
         <v>32.08000183105469</v>
@@ -5491,7 +5491,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>30.39900970458984</v>
+        <v>30.39900779724121</v>
       </c>
       <c r="C189" t="n">
         <v>32.52999877929688</v>
@@ -5549,7 +5549,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>33.80055999755859</v>
+        <v>33.80055618286133</v>
       </c>
       <c r="C191" t="n">
         <v>36.16999816894531</v>
@@ -5578,7 +5578,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>32.47438049316406</v>
+        <v>32.47436904907227</v>
       </c>
       <c r="C192" t="n">
         <v>34.65999984741211</v>
@@ -5607,7 +5607,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>35.22898483276367</v>
+        <v>35.2289924621582</v>
       </c>
       <c r="C193" t="n">
         <v>37.59999847412109</v>
@@ -5636,7 +5636,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>32.06212997436523</v>
+        <v>32.0621337890625</v>
       </c>
       <c r="C194" t="n">
         <v>34.22000122070312</v>
@@ -5665,7 +5665,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>31.86652183532715</v>
+        <v>31.86651802062988</v>
       </c>
       <c r="C195" t="n">
         <v>33.90999984741211</v>
@@ -5694,7 +5694,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>35.19319152832031</v>
+        <v>35.19318771362305</v>
       </c>
       <c r="C196" t="n">
         <v>37.45000076293945</v>
@@ -5752,7 +5752,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>29.96916770935059</v>
+        <v>29.96916961669922</v>
       </c>
       <c r="C198" t="n">
         <v>31.79000091552734</v>
@@ -5781,7 +5781,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>27.39553642272949</v>
+        <v>27.39553260803223</v>
       </c>
       <c r="C199" t="n">
         <v>29.05999946594238</v>
@@ -5839,7 +5839,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>29.92865753173828</v>
+        <v>29.92865180969238</v>
       </c>
       <c r="C201" t="n">
         <v>31.64999961853027</v>
@@ -5868,7 +5868,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>25.19113159179688</v>
+        <v>25.19113349914551</v>
       </c>
       <c r="C202" t="n">
         <v>26.63999938964844</v>
@@ -5897,7 +5897,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>27.47951698303223</v>
+        <v>27.47951889038086</v>
       </c>
       <c r="C203" t="n">
         <v>29.05999946594238</v>
@@ -5926,7 +5926,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>31.00991058349609</v>
+        <v>31.00991439819336</v>
       </c>
       <c r="C204" t="n">
         <v>32.68999862670898</v>
@@ -5984,7 +5984,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>29.33088874816895</v>
+        <v>29.33088684082031</v>
       </c>
       <c r="C206" t="n">
         <v>30.92000007629395</v>
@@ -6013,7 +6013,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>29.02681922912598</v>
+        <v>29.02682113647461</v>
       </c>
       <c r="C207" t="n">
         <v>30.48999977111816</v>
@@ -6042,7 +6042,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>28.50321769714355</v>
+        <v>28.50321578979492</v>
       </c>
       <c r="C208" t="n">
         <v>29.94000053405762</v>
@@ -6071,7 +6071,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>29.16962242126465</v>
+        <v>29.16962051391602</v>
       </c>
       <c r="C209" t="n">
         <v>30.63999938964844</v>
@@ -6129,7 +6129,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>32.57989501953125</v>
+        <v>32.57989883422852</v>
       </c>
       <c r="C211" t="n">
         <v>34.09999847412109</v>
@@ -6187,7 +6187,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>28.95733833312988</v>
+        <v>28.95734024047852</v>
       </c>
       <c r="C213" t="n">
         <v>30.20000076293945</v>
@@ -6216,7 +6216,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>29.48470687866211</v>
+        <v>29.48471069335938</v>
       </c>
       <c r="C214" t="n">
         <v>30.75</v>
@@ -6274,7 +6274,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>31.07759094238281</v>
+        <v>31.07758903503418</v>
       </c>
       <c r="C216" t="n">
         <v>32.29999923706055</v>
@@ -6332,7 +6332,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>34.34892272949219</v>
+        <v>34.34891510009766</v>
       </c>
       <c r="C218" t="n">
         <v>35.70000076293945</v>
@@ -6390,7 +6390,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>35.78017807006836</v>
+        <v>35.78018188476562</v>
       </c>
       <c r="C220" t="n">
         <v>37.06999969482422</v>
@@ -6419,7 +6419,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>32.06413650512695</v>
+        <v>32.06414031982422</v>
       </c>
       <c r="C221" t="n">
         <v>33.22000122070312</v>
@@ -6448,7 +6448,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>32.69351577758789</v>
+        <v>32.69351196289062</v>
       </c>
       <c r="C222" t="n">
         <v>33.75</v>
@@ -6506,7 +6506,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>34.00124359130859</v>
+        <v>34.00124740600586</v>
       </c>
       <c r="C224" t="n">
         <v>35.09999847412109</v>
@@ -6564,7 +6564,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>33.56777191162109</v>
+        <v>33.56777572631836</v>
       </c>
       <c r="C226" t="n">
         <v>34.52999877929688</v>
@@ -6622,7 +6622,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>35.64842987060547</v>
+        <v>35.64843368530273</v>
       </c>
       <c r="C228" t="n">
         <v>36.54999923706055</v>
@@ -6651,7 +6651,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>31.4740047454834</v>
+        <v>31.47400093078613</v>
       </c>
       <c r="C229" t="n">
         <v>32.27000045776367</v>
@@ -6709,7 +6709,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>31.34772872924805</v>
+        <v>31.34772682189941</v>
       </c>
       <c r="C231" t="n">
         <v>32.0099983215332</v>
@@ -6738,7 +6738,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>28.82110786437988</v>
+        <v>28.82110595703125</v>
       </c>
       <c r="C232" t="n">
         <v>29.43000030517578</v>
@@ -6767,7 +6767,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>27.48924255371094</v>
+        <v>27.48924446105957</v>
       </c>
       <c r="C233" t="n">
         <v>28.06999969482422</v>
@@ -6854,7 +6854,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>34.94929504394531</v>
+        <v>34.94929885864258</v>
       </c>
       <c r="C236" t="n">
         <v>35.54000091552734</v>
@@ -6883,7 +6883,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>32.09741592407227</v>
+        <v>32.09741973876953</v>
       </c>
       <c r="C237" t="n">
         <v>32.5099983215332</v>
@@ -6912,7 +6912,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>35.05934143066406</v>
+        <v>35.05934524536133</v>
       </c>
       <c r="C238" t="n">
         <v>35.5099983215332</v>
